--- a/apps/api/assets/vocabulary/小学/人教版/三年级下.xlsx
+++ b/apps/api/assets/vocabulary/小学/人教版/三年级下.xlsx
@@ -440,7 +440,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D72"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
@@ -522,6 +522,16 @@
           <t>USA</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>abbr. 美国；美利坚合众国（the United States of America）</t>
